--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260929.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260929.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>4.02%</t>
         </is>
       </c>
     </row>
@@ -660,51 +660,51 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>51,253,000</t>
+          <t>6,390,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>6,390,000</t>
+          <t>51,253,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>2.99%</t>
         </is>
       </c>
     </row>
@@ -777,39 +777,39 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>27,928,000</t>
+          <t>21,845,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>21,845,000</t>
+          <t>27,928,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -843,39 +843,39 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>33,426,000</t>
+          <t>3,843,058,675</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>36,729,000</t>
+          <t>33,426,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,132 +887,132 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>漢唐集成</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>3,008,000</t>
+          <t>36,729,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,843,058,675</t>
+          <t>6,990,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>漢唐集成</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>6,990,000</t>
+          <t>3,008,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>585,000</t>
+          <t>10,091,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>10,091,000</t>
+          <t>4,101,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.33%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>4,101,000</t>
+          <t>585,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -1056,90 +1056,90 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>42,300,500</t>
+          <t>18,807,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>4,409,000</t>
+          <t>42,300,500</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>18,807,000</t>
+          <t>4,409,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>4,784,400</t>
+          <t>14,684,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,22 +1151,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>14,684,000</t>
+          <t>4,784,400</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,826,381,204</t>
+          <t>2,788,541,204</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
@@ -1298,46 +1298,46 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.70%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>42,169,000</t>
+          <t>10,015,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>10,015,000</t>
+          <t>42,169,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,39 +1349,39 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>10,287,000</t>
+          <t>6,478,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>6,478,000</t>
+          <t>10,287,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,44 +1393,44 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,991,000</t>
+          <t>9,344,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>9,344,000</t>
+          <t>7,991,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.35%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
